--- a/utilities/genetic_diversity/genetic_diversity_r/RSV_diversity_results.xlsx
+++ b/utilities/genetic_diversity/genetic_diversity_r/RSV_diversity_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arimaite/Documents/GitHub/RSV-wastewater-2024-2025/utilities/genetic_diversity/genetic_diversity_r/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D654BC-5FED-D14B-816F-7276C514E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40031C54-1EF3-A84F-8282-23CDA9D10807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="600" windowWidth="26800" windowHeight="15080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13520" yWindow="3140" windowWidth="15280" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marginal_means" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="36">
   <si>
     <t>comparison_type</t>
   </si>
@@ -53,13 +53,10 @@
     <t>Whole genome</t>
   </si>
   <si>
-    <t>Shannon entropy</t>
+    <t>Nucleotide diversity</t>
   </si>
   <si>
     <t>RSV_B</t>
-  </si>
-  <si>
-    <t>Nucleotide diversity</t>
   </si>
   <si>
     <t>Subtype, gene level</t>
@@ -164,7 +161,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -196,16 +193,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,14 +505,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" customWidth="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -529,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -561,13 +557,13 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>5.47E-3</v>
+        <v>3.62E-3</v>
       </c>
       <c r="G2">
-        <v>4.6499999999999996E-3</v>
+        <v>3.0300000000000001E-3</v>
       </c>
       <c r="H2">
-        <v>6.45E-3</v>
+        <v>4.3099999999999996E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -584,64 +580,64 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>2.7000000000000001E-3</v>
+        <v>1.7700000000000001E-3</v>
       </c>
       <c r="G3">
-        <v>2.2300000000000002E-3</v>
+        <v>1.4400000000000001E-3</v>
       </c>
       <c r="H3">
-        <v>3.2499999999999999E-3</v>
+        <v>2.16E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4">
+        <v>2.4499999999999999E-3</v>
+      </c>
+      <c r="G4">
+        <v>1.67E-3</v>
+      </c>
+      <c r="H4">
         <v>3.62E-3</v>
-      </c>
-      <c r="G4">
-        <v>3.0300000000000001E-3</v>
-      </c>
-      <c r="H4">
-        <v>4.3099999999999996E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>1.7700000000000001E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="G5">
-        <v>1.4400000000000001E-3</v>
+        <v>5.6999999999999998E-4</v>
       </c>
       <c r="H5">
-        <v>2.16E-3</v>
+        <v>1.1100000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -653,18 +649,18 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>3.64E-3</v>
+        <v>4.9199999999999999E-3</v>
       </c>
       <c r="G6">
-        <v>2.5799999999999998E-3</v>
+        <v>3.9199999999999999E-3</v>
       </c>
       <c r="H6">
-        <v>5.1399999999999996E-3</v>
+        <v>6.1799999999999997E-3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -676,426 +672,196 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>1.2999999999999999E-3</v>
+        <v>4.8799999999999998E-3</v>
       </c>
       <c r="G7">
-        <v>9.7000000000000005E-4</v>
+        <v>3.7699999999999999E-3</v>
       </c>
       <c r="H7">
-        <v>1.75E-3</v>
+        <v>6.3299999999999997E-3</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>7.7299999999999999E-3</v>
+        <v>2.6700000000000001E-3</v>
       </c>
       <c r="G8">
-        <v>6.3200000000000001E-3</v>
+        <v>1.9599999999999999E-3</v>
       </c>
       <c r="H8">
-        <v>9.4599999999999997E-3</v>
+        <v>3.63E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>7.3899999999999999E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="G9">
-        <v>5.8799999999999998E-3</v>
+        <v>3.8700000000000002E-3</v>
       </c>
       <c r="H9">
-        <v>9.2899999999999996E-3</v>
+        <v>5.96E-3</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>2.4499999999999999E-3</v>
+        <v>7.7999999999999999E-4</v>
       </c>
       <c r="G10">
-        <v>1.67E-3</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="H10">
-        <v>3.62E-3</v>
+        <v>1.08E-3</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>8.0000000000000004E-4</v>
+        <v>4.5399999999999998E-3</v>
       </c>
       <c r="G11">
-        <v>5.6999999999999998E-4</v>
+        <v>3.2699999999999999E-3</v>
       </c>
       <c r="H11">
-        <v>1.1100000000000001E-3</v>
+        <v>6.3099999999999996E-3</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>4.9199999999999999E-3</v>
+        <v>15.014570000000001</v>
       </c>
       <c r="G12">
-        <v>3.9199999999999999E-3</v>
+        <v>13.916729999999999</v>
       </c>
       <c r="H12">
-        <v>6.1799999999999997E-3</v>
+        <v>16.199020000000001</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>4.8799999999999998E-3</v>
+        <v>38.41339</v>
       </c>
       <c r="G13">
-        <v>3.7699999999999999E-3</v>
+        <v>36.318629999999999</v>
       </c>
       <c r="H13">
-        <v>6.3299999999999997E-3</v>
+        <v>40.628979999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>3.9699999999999996E-3</v>
+        <v>12.16433</v>
       </c>
       <c r="G14">
-        <v>3.0200000000000001E-3</v>
+        <v>11.24104</v>
       </c>
       <c r="H14">
-        <v>5.2100000000000002E-3</v>
+        <v>13.16344</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>7.5700000000000003E-3</v>
+        <v>32.823839999999997</v>
       </c>
       <c r="G15">
-        <v>6.2399999999999999E-3</v>
+        <v>30.324359999999999</v>
       </c>
       <c r="H15">
-        <v>9.1699999999999993E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <v>1.2700000000000001E-3</v>
-      </c>
-      <c r="G16">
-        <v>9.5E-4</v>
-      </c>
-      <c r="H16">
-        <v>1.7099999999999999E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17">
-        <v>6.8399999999999997E-3</v>
-      </c>
-      <c r="G17">
-        <v>5.0899999999999999E-3</v>
-      </c>
-      <c r="H17">
-        <v>9.1900000000000003E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18">
-        <v>2.6700000000000001E-3</v>
-      </c>
-      <c r="G18">
-        <v>1.9599999999999999E-3</v>
-      </c>
-      <c r="H18">
-        <v>3.63E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19">
-        <v>4.7999999999999996E-3</v>
-      </c>
-      <c r="G19">
-        <v>3.8700000000000002E-3</v>
-      </c>
-      <c r="H19">
-        <v>5.96E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20">
-        <v>7.7999999999999999E-4</v>
-      </c>
-      <c r="G20">
-        <v>5.5999999999999995E-4</v>
-      </c>
-      <c r="H20">
-        <v>1.08E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21">
-        <v>4.5399999999999998E-3</v>
-      </c>
-      <c r="G21">
-        <v>3.2699999999999999E-3</v>
-      </c>
-      <c r="H21">
-        <v>6.3099999999999996E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22">
-        <v>15.014570000000001</v>
-      </c>
-      <c r="G22">
-        <v>13.916729999999999</v>
-      </c>
-      <c r="H22">
-        <v>16.199020000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23">
-        <v>38.41339</v>
-      </c>
-      <c r="G23">
-        <v>36.318629999999999</v>
-      </c>
-      <c r="H23">
-        <v>40.628979999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24">
-        <v>12.16433</v>
-      </c>
-      <c r="G24">
-        <v>11.24104</v>
-      </c>
-      <c r="H24">
-        <v>13.16344</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25">
-        <v>32.823839999999997</v>
-      </c>
-      <c r="G25">
-        <v>30.324359999999999</v>
-      </c>
-      <c r="H25">
         <v>35.529339999999998</v>
       </c>
     </row>
@@ -1106,50 +872,44 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1157,63 +917,63 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2">
+        <v>2.0477408197967648</v>
+      </c>
+      <c r="F2">
+        <v>0.20865111077326129</v>
+      </c>
+      <c r="G2">
+        <v>7.0341917000867911</v>
+      </c>
+      <c r="H2">
+        <v>2.0041942028727439E-12</v>
+      </c>
+      <c r="I2">
+        <v>2.0041942028727439E-12</v>
+      </c>
+      <c r="J2" t="s">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>2.0302841272258672</v>
-      </c>
-      <c r="F2">
-        <v>0.19381471792326721</v>
-      </c>
-      <c r="G2">
-        <v>7.4184148379416976</v>
-      </c>
-      <c r="H2">
-        <v>1.185303524631398E-13</v>
-      </c>
-      <c r="I2">
-        <v>2.3706070492627959E-13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3">
+        <v>3.0772693070939439</v>
+      </c>
+      <c r="F3">
+        <v>0.68392320684195607</v>
+      </c>
+      <c r="G3">
+        <v>5.0575588089332877</v>
+      </c>
+      <c r="H3">
+        <v>4.246574927312364E-7</v>
+      </c>
+      <c r="I3">
+        <v>8.4931498546247279E-7</v>
+      </c>
+      <c r="J3" t="s">
         <v>32</v>
       </c>
-      <c r="E3">
-        <v>2.0477408197967648</v>
-      </c>
-      <c r="F3">
-        <v>0.20865111077326129</v>
-      </c>
-      <c r="G3">
-        <v>7.0341917000867911</v>
-      </c>
-      <c r="H3">
-        <v>2.0041942028727439E-12</v>
-      </c>
-      <c r="I3">
-        <v>2.0041942028727439E-12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1221,308 +981,151 @@
       <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>1.007248164337557</v>
+      </c>
+      <c r="F4">
+        <v>0.175160299779692</v>
+      </c>
+      <c r="G4">
+        <v>4.1529781885824318E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.96687355081699644</v>
+      </c>
+      <c r="I4">
+        <v>0.96687355081699644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>0.55548767163941926</v>
+      </c>
+      <c r="F5">
+        <v>0.1051317691707024</v>
+      </c>
+      <c r="G5">
+        <v>-3.106350518514343</v>
+      </c>
+      <c r="H5">
+        <v>1.8941204627118749E-3</v>
+      </c>
+      <c r="I5">
+        <v>1.8941204627118749E-3</v>
+      </c>
+      <c r="J5" t="s">
         <v>32</v>
       </c>
-      <c r="E4">
-        <v>2.8003669517251319</v>
-      </c>
-      <c r="F4">
-        <v>0.53768968896159941</v>
-      </c>
-      <c r="G4">
-        <v>5.3630918049907326</v>
-      </c>
-      <c r="H4">
-        <v>8.1809399777287122E-8</v>
-      </c>
-      <c r="I4">
-        <v>3.2723759910914849E-7</v>
-      </c>
-      <c r="J4" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>0.17128351181869919</v>
+      </c>
+      <c r="F6">
+        <v>3.1529438386845771E-2</v>
+      </c>
+      <c r="G6">
+        <v>-9.585284774092754</v>
+      </c>
+      <c r="H6">
+        <v>9.2202933300534612E-22</v>
+      </c>
+      <c r="I6">
+        <v>1.229372444007128E-21</v>
+      </c>
+      <c r="J6" t="s">
         <v>32</v>
       </c>
-      <c r="E5">
-        <v>1.046183245857945</v>
-      </c>
-      <c r="F5">
-        <v>0.16014230601576709</v>
-      </c>
-      <c r="G5">
-        <v>0.29494794179368811</v>
-      </c>
-      <c r="H5">
-        <v>0.76803364785426809</v>
-      </c>
-      <c r="I5">
-        <v>0.96687355081699644</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>0.3908681535417583</v>
+      </c>
+      <c r="F7">
+        <v>1.815633275743915E-2</v>
+      </c>
+      <c r="G7">
+        <v>-20.223008530598971</v>
+      </c>
+      <c r="H7">
+        <v>6.1420815926274584E-91</v>
+      </c>
+      <c r="I7">
+        <v>1.2284163185254919E-90</v>
+      </c>
+      <c r="J7" t="s">
         <v>32</v>
       </c>
-      <c r="E6">
-        <v>3.0772693070939439</v>
-      </c>
-      <c r="F6">
-        <v>0.68392320684195607</v>
-      </c>
-      <c r="G6">
-        <v>5.0575588089332877</v>
-      </c>
-      <c r="H6">
-        <v>4.246574927312364E-7</v>
-      </c>
-      <c r="I6">
-        <v>8.4931498546247279E-7</v>
-      </c>
-      <c r="J6" t="s">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>0.37059429412587808</v>
+      </c>
+      <c r="F8">
+        <v>1.7641988845173869E-2</v>
+      </c>
+      <c r="G8">
+        <v>-20.851926135033921</v>
+      </c>
+      <c r="H8">
+        <v>1.464088204726372E-96</v>
+      </c>
+      <c r="I8">
+        <v>5.8563528189054862E-96</v>
+      </c>
+      <c r="J8" t="s">
         <v>32</v>
-      </c>
-      <c r="E7">
-        <v>1.007248164337557</v>
-      </c>
-      <c r="F7">
-        <v>0.175160299779692</v>
-      </c>
-      <c r="G7">
-        <v>4.1529781885824318E-2</v>
-      </c>
-      <c r="H7">
-        <v>0.96687355081699644</v>
-      </c>
-      <c r="I7">
-        <v>0.96687355081699644</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8">
-        <v>0.52440528414644816</v>
-      </c>
-      <c r="F8">
-        <v>8.7873589351269668E-2</v>
-      </c>
-      <c r="G8">
-        <v>-3.852108530590153</v>
-      </c>
-      <c r="H8">
-        <v>1.171050961962216E-4</v>
-      </c>
-      <c r="I8">
-        <v>1.405261154354659E-4</v>
-      </c>
-      <c r="J8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9">
-        <v>0.18625716469909381</v>
-      </c>
-      <c r="F9">
-        <v>2.979157754211453E-2</v>
-      </c>
-      <c r="G9">
-        <v>-10.507292236486149</v>
-      </c>
-      <c r="H9">
-        <v>7.9956309288217954E-26</v>
-      </c>
-      <c r="I9">
-        <v>1.5991261857643591E-25</v>
-      </c>
-      <c r="J9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10">
-        <v>0.55548767163941926</v>
-      </c>
-      <c r="F10">
-        <v>0.1051317691707024</v>
-      </c>
-      <c r="G10">
-        <v>-3.106350518514343</v>
-      </c>
-      <c r="H10">
-        <v>1.8941204627118749E-3</v>
-      </c>
-      <c r="I10">
-        <v>1.8941204627118749E-3</v>
-      </c>
-      <c r="J10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11">
-        <v>0.17128351181869919</v>
-      </c>
-      <c r="F11">
-        <v>3.1529438386845771E-2</v>
-      </c>
-      <c r="G11">
-        <v>-9.585284774092754</v>
-      </c>
-      <c r="H11">
-        <v>9.2202933300534612E-22</v>
-      </c>
-      <c r="I11">
-        <v>1.383043999508019E-21</v>
-      </c>
-      <c r="J11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12">
-        <v>0.3908681535417583</v>
-      </c>
-      <c r="F12">
-        <v>1.815633275743915E-2</v>
-      </c>
-      <c r="G12">
-        <v>-20.223008530598971</v>
-      </c>
-      <c r="H12">
-        <v>6.1420815926274584E-91</v>
-      </c>
-      <c r="I12">
-        <v>1.8426244777882379E-90</v>
-      </c>
-      <c r="J12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13">
-        <v>0.37059429412587808</v>
-      </c>
-      <c r="F13">
-        <v>1.7641988845173869E-2</v>
-      </c>
-      <c r="G13">
-        <v>-20.851926135033921</v>
-      </c>
-      <c r="H13">
-        <v>1.464088204726372E-96</v>
-      </c>
-      <c r="I13">
-        <v>8.7845292283582293E-96</v>
-      </c>
-      <c r="J13" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
